--- a/output/pdf_financials_xlsx/SICO.xlsx
+++ b/output/pdf_financials_xlsx/SICO.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.066082</v>
+        <v>-5.066082</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>17.797975</v>
+        <v>-17.797975</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.066082</v>
+        <v>-5.066082</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17.797975</v>
+        <v>-17.797975</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.066082</v>
+        <v>-5.066082</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17.797975</v>
+        <v>-17.797975</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>23.027645</v>
+        <v>-23.027645</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>28.250754</v>
+        <v>-28.250754</v>
       </c>
     </row>
     <row r="27">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.066082</v>
+        <v>-5.066082</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>17.797975</v>
+        <v>-17.797975</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.134117</v>
+        <v>-4.998047</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>18.021722</v>
+        <v>-17.574228</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.809881</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.807192</v>
       </c>
     </row>
     <row r="93">
@@ -2680,7 +2680,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>1.809881</v>
       </c>
@@ -4438,10 +4442,10 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>5.066082</v>
+        <v>-5.066082</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>17.797975</v>
+        <v>-17.797975</v>
       </c>
     </row>
     <row r="84">
@@ -4490,10 +4494,10 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>5.415175</v>
+        <v>-5.415175</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>17.47186</v>
+        <v>-17.47186</v>
       </c>
     </row>
     <row r="86">

--- a/output/pdf_financials_xlsx/SICO.xlsx
+++ b/output/pdf_financials_xlsx/SICO.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.031948</v>
+        <v>5.165216</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.51573</v>
+        <v>14.793979</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.031948</v>
+        <v>-5.165216</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.51573</v>
+        <v>-14.793979</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.013767</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-5.066082</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-17.797975</v>
+        <v>-17.811742</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-4.998047</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-17.574228</v>
+        <v>-17.587995</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.00205</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.124955</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.00205</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.124955</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.054245</v>
+        <v>0.052195</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.370178</v>
+        <v>0.245223</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">

--- a/output/pdf_financials_xlsx/SICO.xlsx
+++ b/output/pdf_financials_xlsx/SICO.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.031948</v>
+        <v>0.274972</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.51573</v>
+        <v>1.379885</v>
       </c>
     </row>
     <row r="8">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-1.01468</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-1.400265</v>
       </c>
     </row>
     <row r="102">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>1.207991</v>
+        <v>0.193311</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.040327</v>
+        <v>-1.359938</v>
       </c>
     </row>
     <row r="107">
@@ -3032,7 +3032,11 @@
           <t>Value added taxes and GST receivable</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>-1.01468</v>
       </c>
@@ -4036,7 +4040,11 @@
           <t>Salaries, benefits and directors’ fees</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>0.243024</v>
       </c>
